--- a/doc/6分厂/装配线/6-1点位信息.xlsx
+++ b/doc/6分厂/装配线/6-1点位信息.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\六分厂6-1#装配线\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\6分厂\装配线\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7695"/>
+    <workbookView windowWidth="19035" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>1600 P/M1400=ABSTOOTH</t>
   </si>
   <si>
-    <t>震动检测结果</t>
+    <t>振动检测结果</t>
   </si>
   <si>
     <t>跳动检测值</t>
@@ -2159,7 +2159,7 @@
       <c r="L18" s="24"/>
       <c r="M18" s="19"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" ht="14.25" spans="1:13">
       <c r="A19" s="25" t="s">
         <v>36</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="L19" s="24"/>
       <c r="M19" s="19"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" ht="14.25" spans="1:13">
       <c r="A20" s="25" t="s">
         <v>36</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="L20" s="24"/>
       <c r="M20" s="19"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" ht="14.25" spans="1:13">
       <c r="A21" s="25" t="s">
         <v>36</v>
       </c>
@@ -2258,7 +2258,7 @@
       <c r="L21" s="52"/>
       <c r="M21" s="50"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" ht="14.25" spans="1:13">
       <c r="A22" s="25" t="s">
         <v>36</v>
       </c>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" ht="14.25" spans="1:13">
       <c r="A23" s="25" t="s">
         <v>36</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" ht="14.25" spans="1:13">
       <c r="A24" s="25" t="s">
         <v>36</v>
       </c>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" ht="14.25" spans="1:13">
       <c r="A25" s="25" t="s">
         <v>36</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" ht="14.25" spans="1:13">
       <c r="A26" s="25" t="s">
         <v>36</v>
       </c>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" ht="14.25" spans="1:13">
       <c r="A27" s="25" t="s">
         <v>36</v>
       </c>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" ht="14.25" spans="1:13">
       <c r="A28" s="25" t="s">
         <v>36</v>
       </c>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" ht="14.25" spans="1:13">
       <c r="A29" s="25" t="s">
         <v>36</v>
       </c>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" ht="14.25" spans="1:13">
       <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="M30" s="19"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" ht="14.25" spans="1:13">
       <c r="A31" s="25" t="s">
         <v>36</v>
       </c>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M34" s="19"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" ht="14.25" spans="1:13">
       <c r="A35" s="25" t="s">
         <v>36</v>
       </c>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" s="19"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" ht="14.25" spans="1:13">
       <c r="A36" s="25" t="s">
         <v>36</v>
       </c>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="M38" s="19"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" ht="14.25" spans="1:13">
       <c r="A39" s="25" t="s">
         <v>36</v>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="M39" s="19"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" ht="14.25" spans="1:13">
       <c r="A40" s="25" t="s">
         <v>36</v>
       </c>
@@ -2947,7 +2947,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="19"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" ht="14.25" spans="1:13">
       <c r="A42" s="25" t="s">
         <v>36</v>
       </c>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="M42" s="19"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" ht="14.25" spans="1:13">
       <c r="A43" s="25" t="s">
         <v>36</v>
       </c>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M43" s="19"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" ht="14.25" spans="1:13">
       <c r="A44" s="25" t="s">
         <v>36</v>
       </c>
@@ -3050,7 +3050,7 @@
       <c r="L44" s="25"/>
       <c r="M44" s="19"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" ht="14.25" spans="1:13">
       <c r="A45" s="25" t="s">
         <v>36</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="M45" s="19"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" ht="14.25" spans="1:13">
       <c r="A46" s="25" t="s">
         <v>36</v>
       </c>
@@ -3118,7 +3118,7 @@
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" ht="14.25" spans="1:13">
       <c r="A47" s="25" t="s">
         <v>36</v>
       </c>

--- a/doc/6分厂/装配线/6-1点位信息.xlsx
+++ b/doc/6分厂/装配线/6-1点位信息.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19035" windowHeight="7695"/>
+    <workbookView windowWidth="19515" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="119">
   <si>
     <t>设备编号</t>
   </si>
@@ -121,9 +121,21 @@
     <t>UInt16</t>
   </si>
   <si>
+    <t>OP700</t>
+  </si>
+  <si>
+    <t>ZP33-10</t>
+  </si>
+  <si>
     <t>B面钢球组差</t>
   </si>
   <si>
+    <t>0P510</t>
+  </si>
+  <si>
+    <t>ZP33-08</t>
+  </si>
+  <si>
     <t>A面钢球注脂量</t>
   </si>
   <si>
@@ -136,6 +148,12 @@
     <t>({0}/1000)</t>
   </si>
   <si>
+    <t>OP230</t>
+  </si>
+  <si>
+    <t>ZP33-05</t>
+  </si>
+  <si>
     <t>B面钢球注脂量</t>
   </si>
   <si>
@@ -184,6 +202,12 @@
     <t>正游隙检测值</t>
   </si>
   <si>
+    <t>OP900</t>
+  </si>
+  <si>
+    <t>ZP33-12</t>
+  </si>
+  <si>
     <t>游隙压力值</t>
   </si>
   <si>
@@ -205,6 +229,12 @@
     <t>磁性圈平行差检测传感器1</t>
   </si>
   <si>
+    <t>0P1000</t>
+  </si>
+  <si>
+    <t>ZP33-13</t>
+  </si>
+  <si>
     <t>磁性圈平行差检测传感器2</t>
   </si>
   <si>
@@ -217,6 +247,12 @@
     <t>端跳值轴</t>
   </si>
   <si>
+    <t>OP1200</t>
+  </si>
+  <si>
+    <t>ZP33-15</t>
+  </si>
+  <si>
     <t>端跳值平面</t>
   </si>
   <si>
@@ -226,6 +262,12 @@
     <t>1400 TQ</t>
   </si>
   <si>
+    <t>OP1400</t>
+  </si>
+  <si>
+    <t>ZP33-17</t>
+  </si>
+  <si>
     <t>1400 M/HIGH</t>
   </si>
   <si>
@@ -244,6 +286,12 @@
     <t>振动检测结果</t>
   </si>
   <si>
+    <t>OP1300</t>
+  </si>
+  <si>
+    <t>ZP33-16</t>
+  </si>
+  <si>
     <t>跳动检测值</t>
   </si>
   <si>
@@ -254,6 +302,12 @@
   </si>
   <si>
     <t>1150 GONO CHECK</t>
+  </si>
+  <si>
+    <t>OP1150</t>
+  </si>
+  <si>
+    <t>ZP33-14</t>
   </si>
   <si>
     <t>A托盘绑定</t>
@@ -1047,7 +1101,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1176,6 +1230,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1533,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1542,16 +1602,16 @@
     <col min="4" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="24.5" style="28" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
-    <col min="8" max="8" width="7.125" customWidth="1"/>
-    <col min="9" max="9" width="10.25" style="39" customWidth="1"/>
-    <col min="10" max="10" width="9.875" customWidth="1"/>
-    <col min="11" max="11" width="7.375" customWidth="1"/>
-    <col min="12" max="12" width="12.625" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="7.125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="39" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="7.375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="12.625" style="23" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:13">
+    <row r="1" ht="14.25" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1592,7 +1652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:13">
+    <row r="2" ht="15" spans="1:15">
       <c r="A2" s="25" t="s">
         <v>13</v>
       </c>
@@ -1625,7 +1685,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
     </row>
-    <row r="3" ht="15" spans="1:13">
+    <row r="3" ht="15" spans="1:15">
       <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
@@ -1658,7 +1718,7 @@
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
     </row>
-    <row r="4" ht="15" spans="1:13">
+    <row r="4" ht="15" spans="1:15">
       <c r="A4" s="25" t="s">
         <v>13</v>
       </c>
@@ -1691,7 +1751,7 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
     </row>
-    <row r="5" ht="15" spans="1:13">
+    <row r="5" ht="15" spans="1:15">
       <c r="A5" s="25" t="s">
         <v>13</v>
       </c>
@@ -1724,7 +1784,7 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
     </row>
-    <row r="6" ht="15" spans="1:13">
+    <row r="6" ht="15" spans="1:15">
       <c r="A6" s="25" t="s">
         <v>13</v>
       </c>
@@ -1757,7 +1817,7 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="7" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A7" s="25" t="s">
         <v>13</v>
       </c>
@@ -1771,7 +1831,7 @@
       <c r="E7" s="31">
         <v>8001</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="43" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="20"/>
@@ -1789,8 +1849,14 @@
       </c>
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="N7" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
@@ -1804,8 +1870,8 @@
       <c r="E8" s="31">
         <v>8001</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>27</v>
+      <c r="F8" s="43" t="s">
+        <v>29</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="17" t="s">
@@ -1822,8 +1888,14 @@
       </c>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A9" s="25" t="s">
         <v>13</v>
       </c>
@@ -1837,8 +1909,8 @@
       <c r="E9" s="31">
         <v>8001</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>28</v>
+      <c r="F9" s="43" t="s">
+        <v>32</v>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="17" t="s">
@@ -1854,11 +1926,17 @@
         <v>1</v>
       </c>
       <c r="L9" s="24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M9" s="19"/>
-    </row>
-    <row r="10" ht="15" spans="1:13">
+      <c r="N9" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:15">
       <c r="A10" s="25" t="s">
         <v>13</v>
       </c>
@@ -1873,7 +1951,7 @@
         <v>8001</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="17" t="s">
@@ -1889,11 +1967,17 @@
         <v>1</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M10" s="19"/>
-    </row>
-    <row r="11" ht="15" spans="1:13">
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:15">
       <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
@@ -1907,8 +1991,8 @@
       <c r="E11" s="31">
         <v>8001</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>32</v>
+      <c r="F11" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
@@ -1924,11 +2008,17 @@
         <v>1</v>
       </c>
       <c r="L11" s="24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M11" s="19"/>
-    </row>
-    <row r="12" ht="15" spans="1:13">
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:15">
       <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
@@ -1943,25 +2033,25 @@
         <v>8001</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G12" s="20"/>
       <c r="H12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="45">
         <v>24070</v>
       </c>
-      <c r="J12" s="44" t="s">
-        <v>34</v>
+      <c r="J12" s="46" t="s">
+        <v>40</v>
       </c>
       <c r="K12" s="20">
         <v>18</v>
       </c>
       <c r="L12" s="24"/>
-      <c r="M12" s="45"/>
-    </row>
-    <row r="13" ht="15" spans="1:13">
+      <c r="M12" s="47"/>
+    </row>
+    <row r="13" ht="15" spans="1:15">
       <c r="A13" s="25" t="s">
         <v>13</v>
       </c>
@@ -1976,33 +2066,33 @@
         <v>8001</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="45">
         <v>24090</v>
       </c>
-      <c r="J13" s="44" t="s">
-        <v>34</v>
+      <c r="J13" s="46" t="s">
+        <v>40</v>
       </c>
       <c r="K13" s="20">
         <v>18</v>
       </c>
       <c r="L13" s="24"/>
-      <c r="M13" s="45"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:13">
+      <c r="M13" s="47"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:15">
       <c r="A14" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19">
@@ -2016,7 +2106,7 @@
         <v>16</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>17</v>
@@ -2027,22 +2117,22 @@
       <c r="L14" s="24"/>
       <c r="M14" s="19"/>
     </row>
-    <row r="15" ht="14.25" spans="1:13">
+    <row r="15" ht="14.25" spans="1:15">
       <c r="A15" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19">
         <v>8002</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="25" t="s">
@@ -2051,8 +2141,8 @@
       <c r="I15" s="20">
         <v>22882</v>
       </c>
-      <c r="J15" s="46" t="s">
-        <v>34</v>
+      <c r="J15" s="48" t="s">
+        <v>40</v>
       </c>
       <c r="K15" s="20">
         <v>32</v>
@@ -2060,22 +2150,22 @@
       <c r="L15" s="18"/>
       <c r="M15" s="39"/>
     </row>
-    <row r="16" ht="14.25" spans="1:13">
+    <row r="16" ht="14.25" spans="1:15">
       <c r="A16" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19">
         <v>8002</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G16" s="20"/>
       <c r="H16" s="17" t="s">
@@ -2093,22 +2183,22 @@
       <c r="L16" s="40"/>
       <c r="M16" s="19"/>
     </row>
-    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:13">
+    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:15">
       <c r="A17" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19">
         <v>8002</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="17" t="s">
@@ -2117,7 +2207,7 @@
       <c r="I17" s="20">
         <v>22801</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="49" t="s">
         <v>26</v>
       </c>
       <c r="K17" s="20">
@@ -2126,22 +2216,22 @@
       <c r="L17" s="24"/>
       <c r="M17" s="19"/>
     </row>
-    <row r="18" s="38" customFormat="1" ht="14.25" spans="1:13">
+    <row r="18" s="38" customFormat="1" ht="14.25" spans="1:15">
       <c r="A18" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19">
         <v>8002</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G18" s="20"/>
       <c r="H18" s="17" t="s">
@@ -2159,22 +2249,22 @@
       <c r="L18" s="24"/>
       <c r="M18" s="19"/>
     </row>
-    <row r="19" ht="14.25" spans="1:13">
+    <row r="19" ht="14.25" spans="1:15">
       <c r="A19" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19">
         <v>8002</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="17" t="s">
@@ -2192,22 +2282,22 @@
       <c r="L19" s="24"/>
       <c r="M19" s="19"/>
     </row>
-    <row r="20" ht="14.25" spans="1:13">
+    <row r="20" ht="14.25" spans="1:15">
       <c r="A20" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19">
         <v>8002</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="17" t="s">
@@ -2225,55 +2315,55 @@
       <c r="L20" s="24"/>
       <c r="M20" s="19"/>
     </row>
-    <row r="21" ht="14.25" spans="1:13">
+    <row r="21" ht="14.25" spans="1:15">
       <c r="A21" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50">
+        <v>42</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52">
         <v>8002</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G21" s="20"/>
-      <c r="H21" s="51" t="s">
+      <c r="H21" s="53" t="s">
         <v>19</v>
       </c>
       <c r="I21" s="20">
         <v>22806</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K21" s="20">
         <v>1</v>
       </c>
-      <c r="L21" s="52"/>
-      <c r="M21" s="50"/>
-    </row>
-    <row r="22" ht="14.25" spans="1:13">
+      <c r="L21" s="54"/>
+      <c r="M21" s="52"/>
+    </row>
+    <row r="22" ht="14.25" spans="1:15">
       <c r="A22" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25">
         <v>8002</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25" t="s">
@@ -2289,26 +2379,32 @@
         <v>1</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M22" s="19"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:13">
+      <c r="N22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:15">
       <c r="A23" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25">
         <v>8002</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G23" s="25"/>
       <c r="H23" s="25" t="s">
@@ -2324,26 +2420,32 @@
         <v>1</v>
       </c>
       <c r="L23" s="24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M23" s="19"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:13">
+      <c r="N23" t="s">
+        <v>54</v>
+      </c>
+      <c r="O23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" spans="1:15">
       <c r="A24" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="25">
         <v>8002</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G24" s="25"/>
       <c r="H24" s="25" t="s">
@@ -2359,26 +2461,32 @@
         <v>1</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M24" s="19"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:13">
+      <c r="N24" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="1:15">
       <c r="A25" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="25">
         <v>8002</v>
       </c>
-      <c r="F25" s="48" t="s">
-        <v>50</v>
+      <c r="F25" s="50" t="s">
+        <v>58</v>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="17" t="s">
@@ -2391,26 +2499,32 @@
         <v>23</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M25" s="19"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:13">
+      <c r="N25" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" spans="1:15">
       <c r="A26" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19">
         <v>8002</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="17" t="s">
@@ -2426,26 +2540,32 @@
         <v>1</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M26" s="19"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:13">
+      <c r="N26" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="1:15">
       <c r="A27" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19">
         <v>8002</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="17" t="s">
@@ -2461,26 +2581,32 @@
         <v>1</v>
       </c>
       <c r="L27" s="24" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M27" s="19"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:13">
+      <c r="N27" t="s">
+        <v>54</v>
+      </c>
+      <c r="O27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:15">
       <c r="A28" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19">
         <v>8002</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="17" t="s">
@@ -2496,26 +2622,32 @@
         <v>1</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M28" s="19"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:13">
+      <c r="N28" t="s">
+        <v>63</v>
+      </c>
+      <c r="O28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="1:15">
       <c r="A29" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19">
         <v>8002</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="17" t="s">
@@ -2531,26 +2663,32 @@
         <v>1</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M29" s="19"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:13">
+      <c r="N29" t="s">
+        <v>63</v>
+      </c>
+      <c r="O29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:15">
       <c r="A30" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19">
         <v>8002</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="17" t="s">
@@ -2566,32 +2704,38 @@
         <v>1</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M30" s="19"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:13">
+      <c r="N30" t="s">
+        <v>63</v>
+      </c>
+      <c r="O30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="1:15">
       <c r="A31" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19">
         <v>8002</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G31" s="20"/>
       <c r="H31" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I31" s="53">
+      <c r="I31" s="55">
         <v>22848</v>
       </c>
       <c r="J31" s="21" t="s">
@@ -2601,26 +2745,32 @@
         <v>1</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M31" s="19"/>
-    </row>
-    <row r="32" customFormat="1" ht="14.25" spans="1:13">
+      <c r="N31" t="s">
+        <v>63</v>
+      </c>
+      <c r="O31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="14.25" spans="1:15">
       <c r="A32" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="25">
         <v>8002</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G32" s="25"/>
       <c r="H32" s="25" t="s">
@@ -2637,23 +2787,29 @@
       </c>
       <c r="L32" s="25"/>
       <c r="M32" s="19"/>
-    </row>
-    <row r="33" customFormat="1" ht="14.25" spans="1:13">
+      <c r="N32" t="s">
+        <v>69</v>
+      </c>
+      <c r="O32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="14.25" spans="1:15">
       <c r="A33" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="25">
         <v>8002</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G33" s="25"/>
       <c r="H33" s="25" t="s">
@@ -2670,23 +2826,29 @@
       </c>
       <c r="L33" s="25"/>
       <c r="M33" s="19"/>
-    </row>
-    <row r="34" customFormat="1" ht="14.25" spans="1:13">
+      <c r="N33" t="s">
+        <v>69</v>
+      </c>
+      <c r="O33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="14.25" spans="1:15">
       <c r="A34" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="25">
         <v>8002</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G34" s="25"/>
       <c r="H34" s="25" t="s">
@@ -2702,26 +2864,32 @@
         <v>1</v>
       </c>
       <c r="L34" s="25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M34" s="19"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:13">
+      <c r="N34" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" spans="1:15">
       <c r="A35" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="25">
         <v>8002</v>
       </c>
-      <c r="F35" s="54" t="s">
-        <v>61</v>
+      <c r="F35" s="56" t="s">
+        <v>73</v>
       </c>
       <c r="G35" s="25"/>
       <c r="H35" s="25" t="s">
@@ -2737,26 +2905,32 @@
         <v>1</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M35" s="19"/>
-    </row>
-    <row r="36" ht="14.25" spans="1:13">
+      <c r="N35" t="s">
+        <v>74</v>
+      </c>
+      <c r="O35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:15">
       <c r="A36" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25">
         <v>8002</v>
       </c>
-      <c r="F36" s="54" t="s">
-        <v>62</v>
+      <c r="F36" s="56" t="s">
+        <v>76</v>
       </c>
       <c r="G36" s="25"/>
       <c r="H36" s="25" t="s">
@@ -2772,26 +2946,32 @@
         <v>1</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M36" s="19"/>
-    </row>
-    <row r="37" ht="27.75" spans="1:13">
+      <c r="N36" t="s">
+        <v>74</v>
+      </c>
+      <c r="O36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" ht="27.75" spans="1:15">
       <c r="A37" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="25">
         <v>8002</v>
       </c>
-      <c r="F37" s="54" t="s">
-        <v>63</v>
+      <c r="F37" s="56" t="s">
+        <v>77</v>
       </c>
       <c r="G37" s="25"/>
       <c r="H37" s="25" t="s">
@@ -2807,26 +2987,32 @@
         <v>1</v>
       </c>
       <c r="L37" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M37" s="19"/>
-    </row>
-    <row r="38" ht="27.75" spans="1:13">
+      <c r="N37" t="s">
+        <v>74</v>
+      </c>
+      <c r="O37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" ht="27.75" spans="1:15">
       <c r="A38" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="25">
         <v>8002</v>
       </c>
-      <c r="F38" s="54" t="s">
-        <v>64</v>
+      <c r="F38" s="56" t="s">
+        <v>78</v>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="25" t="s">
@@ -2842,26 +3028,32 @@
         <v>1</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M38" s="19"/>
-    </row>
-    <row r="39" ht="14.25" spans="1:13">
+      <c r="N38" t="s">
+        <v>74</v>
+      </c>
+      <c r="O38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" spans="1:15">
       <c r="A39" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="25">
         <v>8002</v>
       </c>
-      <c r="F39" s="54" t="s">
-        <v>65</v>
+      <c r="F39" s="56" t="s">
+        <v>79</v>
       </c>
       <c r="G39" s="25"/>
       <c r="H39" s="25" t="s">
@@ -2877,26 +3069,32 @@
         <v>1</v>
       </c>
       <c r="L39" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M39" s="19"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:13">
+      <c r="N39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" spans="1:15">
       <c r="A40" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="25">
         <v>8002</v>
       </c>
-      <c r="F40" s="54" t="s">
-        <v>66</v>
+      <c r="F40" s="56" t="s">
+        <v>80</v>
       </c>
       <c r="G40" s="25"/>
       <c r="H40" s="25" t="s">
@@ -2913,23 +3111,29 @@
       </c>
       <c r="L40" s="25"/>
       <c r="M40" s="19"/>
-    </row>
-    <row r="41" ht="15" spans="1:13">
+      <c r="N40" t="s">
+        <v>74</v>
+      </c>
+      <c r="O40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:15">
       <c r="A41" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="25">
         <v>8002</v>
       </c>
-      <c r="F41" s="54" t="s">
-        <v>67</v>
+      <c r="F41" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="G41" s="25"/>
       <c r="H41" s="31" t="s">
@@ -2946,23 +3150,29 @@
       </c>
       <c r="L41" s="25"/>
       <c r="M41" s="19"/>
-    </row>
-    <row r="42" ht="14.25" spans="1:13">
+      <c r="N41" t="s">
+        <v>82</v>
+      </c>
+      <c r="O41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" spans="1:15">
       <c r="A42" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D42" s="25"/>
       <c r="E42" s="25">
         <v>8002</v>
       </c>
-      <c r="F42" s="54" t="s">
-        <v>68</v>
+      <c r="F42" s="56" t="s">
+        <v>84</v>
       </c>
       <c r="G42" s="25"/>
       <c r="H42" s="25" t="s">
@@ -2978,26 +3188,32 @@
         <v>1</v>
       </c>
       <c r="L42" s="25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M42" s="19"/>
-    </row>
-    <row r="43" ht="14.25" spans="1:13">
+      <c r="N42" t="s">
+        <v>69</v>
+      </c>
+      <c r="O42" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" spans="1:15">
       <c r="A43" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="25">
         <v>8002</v>
       </c>
-      <c r="F43" s="54" t="s">
-        <v>69</v>
+      <c r="F43" s="56" t="s">
+        <v>85</v>
       </c>
       <c r="G43" s="25"/>
       <c r="H43" s="25" t="s">
@@ -3013,26 +3229,26 @@
         <v>1</v>
       </c>
       <c r="L43" s="25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M43" s="19"/>
     </row>
-    <row r="44" ht="14.25" spans="1:13">
+    <row r="44" ht="14.25" spans="1:15">
       <c r="A44" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="25">
         <v>8002</v>
       </c>
-      <c r="F44" s="54" t="s">
-        <v>70</v>
+      <c r="F44" s="56" t="s">
+        <v>86</v>
       </c>
       <c r="G44" s="25"/>
       <c r="H44" s="25" t="s">
@@ -3050,22 +3266,22 @@
       <c r="L44" s="25"/>
       <c r="M44" s="19"/>
     </row>
-    <row r="45" ht="14.25" spans="1:13">
+    <row r="45" ht="14.25" spans="1:15">
       <c r="A45" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25">
         <v>8002</v>
       </c>
-      <c r="F45" s="54" t="s">
-        <v>71</v>
+      <c r="F45" s="56" t="s">
+        <v>87</v>
       </c>
       <c r="G45" s="25"/>
       <c r="H45" s="25" t="s">
@@ -3081,26 +3297,32 @@
         <v>1</v>
       </c>
       <c r="L45" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M45" s="19"/>
-    </row>
-    <row r="46" ht="14.25" spans="1:13">
+      <c r="N45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" spans="1:15">
       <c r="A46" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="25">
         <v>8002</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="25" t="s">
@@ -3118,22 +3340,22 @@
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
     </row>
-    <row r="47" ht="14.25" spans="1:13">
+    <row r="47" ht="14.25" spans="1:15">
       <c r="A47" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="25">
         <v>8002</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G47" s="19"/>
       <c r="H47" s="25" t="s">
@@ -3175,16 +3397,16 @@
     <row r="1" ht="14.25"/>
     <row r="2" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C2" s="6">
         <v>9004</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="4" t="s">
@@ -3192,7 +3414,7 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
@@ -3203,16 +3425,16 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3" s="6">
         <v>9004</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
@@ -3220,7 +3442,7 @@
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -3231,16 +3453,16 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="14.25" spans="1:12">
       <c r="A4" s="12" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C4" s="13">
         <v>9004</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
@@ -3260,16 +3482,16 @@
     <row r="5" customFormat="1" ht="14.25" hidden="1"/>
     <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C6" s="19">
         <v>9004</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E6" s="20"/>
       <c r="F6" s="17" t="s">
@@ -3277,7 +3499,7 @@
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="21" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
@@ -3288,16 +3510,16 @@
     </row>
     <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C7" s="19">
         <v>9004</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="17" t="s">
@@ -3305,7 +3527,7 @@
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="21" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
@@ -3316,16 +3538,16 @@
     </row>
     <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" s="19">
         <v>9004</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="17" t="s">
@@ -3344,16 +3566,16 @@
     </row>
     <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C9" s="19">
         <v>9004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="17" t="s">
@@ -3367,23 +3589,23 @@
         <v>1</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="19"/>
     </row>
     <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C10" s="19">
         <v>9004</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E10" s="20"/>
       <c r="F10" s="17" t="s">
@@ -3397,23 +3619,23 @@
         <v>1</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="19"/>
     </row>
     <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C11" s="19">
         <v>9004</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E11" s="20"/>
       <c r="F11" s="17" t="s">
@@ -3427,23 +3649,23 @@
         <v>1</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="19"/>
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C12" s="19">
         <v>9004</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="17" t="s">
@@ -3457,27 +3679,27 @@
         <v>1</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="19"/>
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="25" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C13" s="19">
         <v>9004</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="18" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="26" t="s">
@@ -3492,7 +3714,7 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A14" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>14</v>
@@ -3501,7 +3723,7 @@
         <v>8001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3513,7 +3735,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A15" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>14</v>
@@ -3522,7 +3744,7 @@
         <v>8001</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3534,7 +3756,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A16" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>14</v>
@@ -3543,7 +3765,7 @@
         <v>8001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3555,7 +3777,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A17" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>14</v>
@@ -3564,7 +3786,7 @@
         <v>8001</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3576,7 +3798,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A18" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>14</v>
@@ -3585,7 +3807,7 @@
         <v>8001</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3597,7 +3819,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A19" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>14</v>
@@ -3606,7 +3828,7 @@
         <v>8001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3618,7 +3840,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A20" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>14</v>
@@ -3627,7 +3849,7 @@
         <v>8001</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3639,7 +3861,7 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A21" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>14</v>
@@ -3648,7 +3870,7 @@
         <v>8001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3660,7 +3882,7 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A22" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>14</v>
@@ -3669,7 +3891,7 @@
         <v>8001</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3681,7 +3903,7 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A23" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>14</v>
@@ -3690,7 +3912,7 @@
         <v>8001</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3702,7 +3924,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A24" s="12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>14</v>
@@ -3711,7 +3933,7 @@
         <v>8001</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3723,7 +3945,7 @@
     </row>
     <row r="25" ht="15" hidden="1" spans="1:12">
       <c r="A25" s="25" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>14</v>
@@ -3732,10 +3954,10 @@
         <v>8001</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="26" t="s">
@@ -3750,16 +3972,16 @@
     </row>
     <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
       <c r="A26" s="32" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C26" s="34">
         <v>9004</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="32" t="s">
@@ -3773,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
